--- a/DEV_BSI/DEV - BSI PSAK413 ENGINE DOC.xlsx
+++ b/DEV_BSI/DEV - BSI PSAK413 ENGINE DOC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ENGINE_REGLA_2.0\DEV_BSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52796732-8AE5-4FF2-BFEC-47D267F0B7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A8BA19-307B-4166-8980-9B454E141C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7AFBC37-B41E-4A7A-8245-B7771EBD4149}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E7AFBC37-B41E-4A7A-8245-B7771EBD4149}"/>
   </bookViews>
   <sheets>
     <sheet name="LIST STORE PROCEDURE - BSI" sheetId="1" r:id="rId1"/>
@@ -358,6 +358,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -369,9 +372,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -394,9 +394,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -434,7 +434,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -540,7 +540,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -682,7 +682,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -690,22 +690,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6602FAD-A310-49F4-9085-1E788FDA3282}">
-  <dimension ref="A1:D39"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="44" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1" hidden="1"/>
+    <col min="3" max="3" width="40.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1796875" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="7"/>
       <c r="C1" s="3" t="s">
         <v>18</v>
       </c>
@@ -713,202 +713,202 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
+        <v>57</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
+        <v>46</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
+        <v>54</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
+      <c r="D6" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
+      <c r="D7" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
       <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
+      <c r="D8" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
       <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
+      <c r="D9" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6"/>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
+      <c r="D10" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="6"/>
       <c r="B11" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
+        <v>53</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>33</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -917,168 +917,168 @@
       <c r="C18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
+      <c r="D18" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
       <c r="B19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
+      <c r="D19" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="8"/>
       <c r="B20" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
+      <c r="D20" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="8"/>
       <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
+      <c r="D21" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="8"/>
       <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
+      <c r="D22" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="8"/>
       <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
+      <c r="D23" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
       <c r="B24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
+      <c r="D24" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="8"/>
       <c r="B25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
+      <c r="D25" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
       <c r="B26" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
+      <c r="D26" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
       <c r="B27" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
+      <c r="D27" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="8"/>
       <c r="B28" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
+      <c r="D28" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="8"/>
       <c r="B29" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="7"/>
+      <c r="D29" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="8"/>
       <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="7"/>
+      <c r="D30" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="8"/>
       <c r="B31" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="D31" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -1087,91 +1087,91 @@
       <c r="C32" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
+      <c r="D32" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="9"/>
       <c r="B33" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
+      <c r="D33" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
       <c r="B34" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
+      <c r="D34" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
       <c r="B35" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
+      <c r="D35" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="9"/>
       <c r="B36" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
+      <c r="D36" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="9"/>
       <c r="B37" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
+      <c r="D37" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
       <c r="B38" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
+      <c r="D38" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="9"/>
       <c r="B39" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="5" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1183,5 +1183,9 @@
     <mergeCell ref="A32:A39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Arial"&amp;8&amp;K2E404D Sensitivity Label: General</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/DEV_BSI/DEV - BSI PSAK413 ENGINE DOC.xlsx
+++ b/DEV_BSI/DEV - BSI PSAK413 ENGINE DOC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ENGINE_REGLA_2.0\DEV_BSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A8BA19-307B-4166-8980-9B454E141C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55B8CEF-37B6-4967-B6F0-5C82BE3D85AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E7AFBC37-B41E-4A7A-8245-B7771EBD4149}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7AFBC37-B41E-4A7A-8245-B7771EBD4149}"/>
   </bookViews>
   <sheets>
     <sheet name="LIST STORE PROCEDURE - BSI" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="81">
   <si>
     <t>STORE PROCEDURE NAME</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>ALTER</t>
+  </si>
+  <si>
+    <t>API KEY</t>
   </si>
 </sst>
 </file>
@@ -394,9 +397,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -434,7 +437,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -540,7 +543,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -682,7 +685,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -690,18 +693,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6602FAD-A310-49F4-9085-1E788FDA3282}">
-  <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:XFD39"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="44" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.453125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.1796875" style="1" hidden="1"/>
+    <col min="3" max="3" width="40.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="49.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16383" width="9.140625" style="1" hidden="1"/>
+    <col min="16384" max="16384" width="39.5703125" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -712,8 +716,11 @@
       <c r="D1" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
@@ -726,8 +733,12 @@
       <c r="D2" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="str">
+        <f>B2&amp;"_DEV"</f>
+        <v>SP_IFRS_STAGE_CONFIG_DEV</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -738,8 +749,12 @@
       <c r="D3" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="str">
+        <f t="shared" ref="E3:E39" si="0">B3&amp;"_DEV"</f>
+        <v>SP_IFRS_PD_RULES_CONFIG_DEV</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="2" t="s">
         <v>10</v>
@@ -750,8 +765,12 @@
       <c r="D4" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EAD_RULES_CONFIG_DEV</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="2" t="s">
         <v>2</v>
@@ -762,8 +781,12 @@
       <c r="D5" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_LIFETIME_RULES_CONFIG_DEV</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="2" t="s">
         <v>11</v>
@@ -774,8 +797,12 @@
       <c r="D6" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_MODEL_DETAIL_EAD_DEV</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -786,8 +813,12 @@
       <c r="D7" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_MODEL_DETAIL_LGD_DEV</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="2" t="s">
         <v>13</v>
@@ -798,8 +829,12 @@
       <c r="D8" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_MODEL_DETAIL_PD_DEV</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="2" t="s">
         <v>14</v>
@@ -810,8 +845,12 @@
       <c r="D9" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_MODEL_DETAIL_PF_DEV</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="2" t="s">
         <v>15</v>
@@ -822,8 +861,12 @@
       <c r="D10" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_MODEL_HEADER_DEV</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="2" t="s">
         <v>1</v>
@@ -834,8 +877,12 @@
       <c r="D11" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_LGD_WORKOUT_RULES_CONFIG_DEV</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -846,8 +893,12 @@
       <c r="D12" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_LGD_RULES_CONFIG_DEV</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
@@ -858,8 +909,12 @@
       <c r="D13" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_SEGMENTATION_MAPPING_DEV</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="2" t="s">
         <v>9</v>
@@ -870,8 +925,12 @@
       <c r="D14" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_DEFAULT_CRITERIA_DEV</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
@@ -882,8 +941,12 @@
       <c r="D15" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_SYNC_PARAM_DEV</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="2" t="s">
         <v>7</v>
@@ -894,8 +957,12 @@
       <c r="D16" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_BUCKET_DETAIL_DEV</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -906,8 +973,12 @@
       <c r="D17" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_BUCKET_HEADER_DEV</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>33</v>
       </c>
@@ -920,8 +991,12 @@
       <c r="D18" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_RULE_DATA_DEV</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="1" t="s">
         <v>20</v>
@@ -932,8 +1007,12 @@
       <c r="D19" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_TM_SCENARIO_DATA_DEV</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="1" t="s">
         <v>21</v>
@@ -944,8 +1023,12 @@
       <c r="D20" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MIGRATION_DETAIL_DEV</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
       <c r="B21" s="1" t="s">
         <v>22</v>
@@ -956,8 +1039,12 @@
       <c r="D21" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_ENR_DEV</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="1" t="s">
         <v>23</v>
@@ -968,8 +1055,12 @@
       <c r="D22" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_ENR_SUM_DEV</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="1" t="s">
         <v>24</v>
@@ -980,8 +1071,12 @@
       <c r="D23" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_FLOWRATE_DEV</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="1" t="s">
         <v>25</v>
@@ -992,8 +1087,12 @@
       <c r="D24" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_FLOWRATE_SUM_DEV</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
       <c r="B25" s="1" t="s">
         <v>26</v>
@@ -1004,8 +1103,12 @@
       <c r="D25" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_ODR_DEV</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="1" t="s">
         <v>27</v>
@@ -1016,8 +1119,12 @@
       <c r="D26" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_FLOWRATE_SMOOTH_DEV</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="1" t="s">
         <v>28</v>
@@ -1028,8 +1135,12 @@
       <c r="D27" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_LINEST_SMOOTHING_DEV</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="1" t="s">
         <v>29</v>
@@ -1040,8 +1151,12 @@
       <c r="D28" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_MMULT_MONTHLY_DEV</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="1" t="s">
         <v>30</v>
@@ -1052,8 +1167,12 @@
       <c r="D29" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_MMULT_DEV</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="1" t="s">
         <v>31</v>
@@ -1064,8 +1183,12 @@
       <c r="D30" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_TERM_STRUCTURE_DEV</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
       <c r="B31" s="1" t="s">
         <v>32</v>
@@ -1076,8 +1199,12 @@
       <c r="D31" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_SYNC_TERM_STRUCTURE_FL_DEV</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>42</v>
       </c>
@@ -1090,8 +1217,12 @@
       <c r="D32" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_MODEL_DEV</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="1" t="s">
         <v>35</v>
@@ -1102,8 +1233,12 @@
       <c r="D33" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_UPDATE_STAGE_DEV</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="1" t="s">
         <v>36</v>
@@ -1114,8 +1249,12 @@
       <c r="D34" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_STAGE_BENCANA_DEV</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
       <c r="B35" s="1" t="s">
         <v>37</v>
@@ -1126,8 +1265,12 @@
       <c r="D35" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_GENERATE_IMA_DEV</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
       <c r="B36" s="1" t="s">
         <v>38</v>
@@ -1138,8 +1281,12 @@
       <c r="D36" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EAD_RESULT_DEV</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
       <c r="B37" s="1" t="s">
         <v>39</v>
@@ -1150,8 +1297,12 @@
       <c r="D37" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_RESULT_DETAIL_DEV</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
       <c r="B38" s="1" t="s">
         <v>40</v>
@@ -1162,8 +1313,12 @@
       <c r="D38" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_RESULT_HEADER_DEV</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
       <c r="B39" s="1" t="s">
         <v>41</v>
@@ -1173,6 +1328,10 @@
       </c>
       <c r="D39" s="5" t="s">
         <v>79</v>
+      </c>
+      <c r="E39" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_UPDATE_IMA_RESULT_DEV</v>
       </c>
     </row>
   </sheetData>

--- a/DEV_BSI/DEV - BSI PSAK413 ENGINE DOC.xlsx
+++ b/DEV_BSI/DEV - BSI PSAK413 ENGINE DOC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ENGINE_REGLA_2.0\DEV_BSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55B8CEF-37B6-4967-B6F0-5C82BE3D85AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734B05B3-C972-4936-A06A-42A480D5FB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7AFBC37-B41E-4A7A-8245-B7771EBD4149}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="80">
   <si>
     <t>STORE PROCEDURE NAME</t>
   </si>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>SP_IFRS_PD_TERM_STRUCTURE</t>
-  </si>
-  <si>
-    <t>SP_IFRS_PD_SYNC_TERM_STRUCTURE_FL</t>
   </si>
   <si>
     <t>PD CALC</t>
@@ -693,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6602FAD-A310-49F4-9085-1E788FDA3282}">
-  <dimension ref="A1:XFD39"/>
+  <dimension ref="A1:XFC38"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
@@ -714,10 +711,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -728,10 +725,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E2" s="1" t="str">
         <f>B2&amp;"_DEV"</f>
@@ -744,13 +741,13 @@
         <v>3</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E3" s="1" t="str">
-        <f t="shared" ref="E3:E39" si="0">B3&amp;"_DEV"</f>
+        <f t="shared" ref="E3:E38" si="0">B3&amp;"_DEV"</f>
         <v>SP_IFRS_PD_RULES_CONFIG_DEV</v>
       </c>
     </row>
@@ -760,10 +757,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E4" s="1" t="str">
         <f t="shared" si="0"/>
@@ -776,10 +773,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5" s="1" t="str">
         <f t="shared" si="0"/>
@@ -792,10 +789,10 @@
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E6" s="1" t="str">
         <f t="shared" si="0"/>
@@ -808,10 +805,10 @@
         <v>12</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E7" s="1" t="str">
         <f t="shared" si="0"/>
@@ -824,10 +821,10 @@
         <v>13</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E8" s="1" t="str">
         <f t="shared" si="0"/>
@@ -840,10 +837,10 @@
         <v>14</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9" s="1" t="str">
         <f t="shared" si="0"/>
@@ -856,10 +853,10 @@
         <v>15</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E10" s="1" t="str">
         <f t="shared" si="0"/>
@@ -872,10 +869,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E11" s="1" t="str">
         <f t="shared" si="0"/>
@@ -888,10 +885,10 @@
         <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E12" s="1" t="str">
         <f t="shared" si="0"/>
@@ -904,10 +901,10 @@
         <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E13" s="1" t="str">
         <f t="shared" si="0"/>
@@ -920,10 +917,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E14" s="1" t="str">
         <f t="shared" si="0"/>
@@ -936,10 +933,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E15" s="1" t="str">
         <f t="shared" si="0"/>
@@ -952,10 +949,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E16" s="1" t="str">
         <f t="shared" si="0"/>
@@ -968,10 +965,10 @@
         <v>8</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E17" s="1" t="str">
         <f t="shared" si="0"/>
@@ -980,16 +977,16 @@
     </row>
     <row r="18" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E18" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1002,10 +999,10 @@
         <v>20</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E19" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1018,10 +1015,10 @@
         <v>21</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E20" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1034,10 +1031,10 @@
         <v>22</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E21" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1050,10 +1047,10 @@
         <v>23</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E22" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1066,10 +1063,10 @@
         <v>24</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E23" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1082,10 +1079,10 @@
         <v>25</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E24" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1098,10 +1095,10 @@
         <v>26</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E25" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1114,10 +1111,10 @@
         <v>27</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E26" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1130,10 +1127,10 @@
         <v>28</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E27" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1146,10 +1143,10 @@
         <v>29</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E28" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1162,10 +1159,10 @@
         <v>30</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E29" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1178,10 +1175,10 @@
         <v>31</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E30" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1189,25 +1186,25 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
+      <c r="A31" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="B31" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>71</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>SP_IFRS_PD_SYNC_TERM_STRUCTURE_FL_DEV</v>
+        <v>SP_IFRS_EIL_MODEL_DEV</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
-        <v>42</v>
-      </c>
+      <c r="A32" s="9"/>
       <c r="B32" s="1" t="s">
         <v>34</v>
       </c>
@@ -1215,11 +1212,11 @@
         <v>72</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E32" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>SP_IFRS_EIL_MODEL_DEV</v>
+        <v>SP_IFRS_UPDATE_STAGE_DEV</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1228,14 +1225,14 @@
         <v>35</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E33" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>SP_IFRS_UPDATE_STAGE_DEV</v>
+        <v>SP_IFRS_STAGE_BENCANA_DEV</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1247,11 +1244,11 @@
         <v>73</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E34" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>SP_IFRS_STAGE_BENCANA_DEV</v>
+        <v>SP_IFRS_EIL_GENERATE_IMA_DEV</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1263,11 +1260,11 @@
         <v>74</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E35" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>SP_IFRS_EIL_GENERATE_IMA_DEV</v>
+        <v>SP_IFRS_EAD_RESULT_DEV</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1279,11 +1276,11 @@
         <v>75</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E36" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>SP_IFRS_EAD_RESULT_DEV</v>
+        <v>SP_IFRS_EIL_RESULT_DETAIL_DEV</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1295,11 +1292,11 @@
         <v>76</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E37" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>SP_IFRS_EIL_RESULT_DETAIL_DEV</v>
+        <v>SP_IFRS_EIL_RESULT_HEADER_DEV</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1308,28 +1305,12 @@
         <v>40</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E38" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>SP_IFRS_EIL_RESULT_HEADER_DEV</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
-      <c r="B39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>SP_IFRS_UPDATE_IMA_RESULT_DEV</v>
       </c>
@@ -1338,8 +1319,8 @@
   <mergeCells count="4">
     <mergeCell ref="A2:A17"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:A31"/>
-    <mergeCell ref="A32:A39"/>
+    <mergeCell ref="A18:A30"/>
+    <mergeCell ref="A31:A38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DEV_BSI/DEV - BSI PSAK413 ENGINE DOC.xlsx
+++ b/DEV_BSI/DEV - BSI PSAK413 ENGINE DOC.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ENGINE_REGLA_2.0\DEV_BSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A8BA19-307B-4166-8980-9B454E141C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7B3057-78BA-455E-8829-30C1A8BB457C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E7AFBC37-B41E-4A7A-8245-B7771EBD4149}"/>
   </bookViews>
   <sheets>
     <sheet name="LIST STORE PROCEDURE - BSI" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="81">
   <si>
     <t>STORE PROCEDURE NAME</t>
   </si>
@@ -265,6 +276,9 @@
   </si>
   <si>
     <t>ALTER</t>
+  </si>
+  <si>
+    <t>API KEY</t>
   </si>
 </sst>
 </file>
@@ -697,11 +711,11 @@
     <col min="2" max="2" width="44" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.453125" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.1796875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.1796875" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="14" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -712,8 +726,11 @@
       <c r="D1" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
@@ -726,8 +743,12 @@
       <c r="D2" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="str">
+        <f>B2&amp;"_DEV"</f>
+        <v>SP_IFRS_STAGE_CONFIG_DEV</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -738,8 +759,12 @@
       <c r="D3" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="str">
+        <f t="shared" ref="E3:E39" si="0">B3&amp;"_DEV"</f>
+        <v>SP_IFRS_PD_RULES_CONFIG_DEV</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="2" t="s">
         <v>10</v>
@@ -750,8 +775,12 @@
       <c r="D4" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EAD_RULES_CONFIG_DEV</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="2" t="s">
         <v>2</v>
@@ -762,8 +791,12 @@
       <c r="D5" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_LIFETIME_RULES_CONFIG_DEV</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="2" t="s">
         <v>11</v>
@@ -774,8 +807,12 @@
       <c r="D6" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_MODEL_DETAIL_EAD_DEV</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -786,8 +823,12 @@
       <c r="D7" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_MODEL_DETAIL_LGD_DEV</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="2" t="s">
         <v>13</v>
@@ -798,8 +839,12 @@
       <c r="D8" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_MODEL_DETAIL_PD_DEV</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="2" t="s">
         <v>14</v>
@@ -810,8 +855,12 @@
       <c r="D9" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_MODEL_DETAIL_PF_DEV</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2" t="s">
         <v>15</v>
@@ -822,8 +871,12 @@
       <c r="D10" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_MODEL_HEADER_DEV</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="2" t="s">
         <v>1</v>
@@ -834,8 +887,12 @@
       <c r="D11" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_LGD_WORKOUT_RULES_CONFIG_DEV</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -846,8 +903,12 @@
       <c r="D12" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_LGD_RULES_CONFIG_DEV</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
@@ -858,8 +919,12 @@
       <c r="D13" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_SEGMENTATION_MAPPING_DEV</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="2" t="s">
         <v>9</v>
@@ -870,8 +935,12 @@
       <c r="D14" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_DEFAULT_CRITERIA_DEV</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
@@ -882,8 +951,12 @@
       <c r="D15" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_SYNC_PARAM_DEV</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="2" t="s">
         <v>7</v>
@@ -894,8 +967,12 @@
       <c r="D16" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_BUCKET_DETAIL_DEV</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -906,8 +983,12 @@
       <c r="D17" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_BUCKET_HEADER_DEV</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>33</v>
       </c>
@@ -920,8 +1001,12 @@
       <c r="D18" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_RULE_DATA_DEV</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
       <c r="B19" s="1" t="s">
         <v>20</v>
@@ -932,8 +1017,12 @@
       <c r="D19" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_TM_SCENARIO_DATA_DEV</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="1" t="s">
         <v>21</v>
@@ -944,8 +1033,12 @@
       <c r="D20" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MIGRATION_DETAIL_DEV</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="1" t="s">
         <v>22</v>
@@ -956,8 +1049,12 @@
       <c r="D21" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_ENR_DEV</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="1" t="s">
         <v>23</v>
@@ -968,8 +1065,12 @@
       <c r="D22" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_ENR_SUM_DEV</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
       <c r="B23" s="1" t="s">
         <v>24</v>
@@ -980,8 +1081,12 @@
       <c r="D23" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_FLOWRATE_DEV</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
       <c r="B24" s="1" t="s">
         <v>25</v>
@@ -992,8 +1097,12 @@
       <c r="D24" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_FLOWRATE_SUM_DEV</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="1" t="s">
         <v>26</v>
@@ -1004,8 +1113,12 @@
       <c r="D25" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_ODR_DEV</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
       <c r="B26" s="1" t="s">
         <v>27</v>
@@ -1016,8 +1129,12 @@
       <c r="D26" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_FLOWRATE_SMOOTH_DEV</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
       <c r="B27" s="1" t="s">
         <v>28</v>
@@ -1028,8 +1145,12 @@
       <c r="D27" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_LINEST_SMOOTHING_DEV</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
       <c r="B28" s="1" t="s">
         <v>29</v>
@@ -1040,8 +1161,12 @@
       <c r="D28" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_MMULT_MONTHLY_DEV</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
       <c r="B29" s="1" t="s">
         <v>30</v>
@@ -1052,8 +1177,12 @@
       <c r="D29" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_MAA_MMULT_DEV</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
       <c r="B30" s="1" t="s">
         <v>31</v>
@@ -1064,8 +1193,12 @@
       <c r="D30" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_TERM_STRUCTURE_DEV</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
       <c r="B31" s="1" t="s">
         <v>32</v>
@@ -1076,8 +1209,12 @@
       <c r="D31" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_PD_SYNC_TERM_STRUCTURE_FL_DEV</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>42</v>
       </c>
@@ -1090,8 +1227,12 @@
       <c r="D32" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_MODEL_DEV</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
       <c r="B33" s="1" t="s">
         <v>35</v>
@@ -1102,8 +1243,12 @@
       <c r="D33" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_UPDATE_STAGE_DEV</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="9"/>
       <c r="B34" s="1" t="s">
         <v>36</v>
@@ -1114,8 +1259,12 @@
       <c r="D34" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_STAGE_BENCANA_DEV</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="9"/>
       <c r="B35" s="1" t="s">
         <v>37</v>
@@ -1126,8 +1275,12 @@
       <c r="D35" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_GENERATE_IMA_DEV</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="9"/>
       <c r="B36" s="1" t="s">
         <v>38</v>
@@ -1138,8 +1291,12 @@
       <c r="D36" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EAD_RESULT_DEV</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="9"/>
       <c r="B37" s="1" t="s">
         <v>39</v>
@@ -1150,8 +1307,12 @@
       <c r="D37" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_RESULT_DETAIL_DEV</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="9"/>
       <c r="B38" s="1" t="s">
         <v>40</v>
@@ -1162,8 +1323,12 @@
       <c r="D38" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_EIL_RESULT_HEADER_DEV</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="9"/>
       <c r="B39" s="1" t="s">
         <v>41</v>
@@ -1173,6 +1338,10 @@
       </c>
       <c r="D39" s="5" t="s">
         <v>79</v>
+      </c>
+      <c r="E39" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SP_IFRS_UPDATE_IMA_RESULT_DEV</v>
       </c>
     </row>
   </sheetData>

--- a/DEV_BSI/DEV - BSI PSAK413 ENGINE DOC.xlsx
+++ b/DEV_BSI/DEV - BSI PSAK413 ENGINE DOC.xlsx
@@ -8,28 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ENGINE_REGLA_2.0\DEV_BSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7B3057-78BA-455E-8829-30C1A8BB457C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A050A9DF-DBC6-4542-B211-CCE0A53ED80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E7AFBC37-B41E-4A7A-8245-B7771EBD4149}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7AFBC37-B41E-4A7A-8245-B7771EBD4149}"/>
   </bookViews>
   <sheets>
     <sheet name="LIST STORE PROCEDURE - BSI" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -360,7 +349,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -387,6 +376,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
@@ -408,9 +400,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -448,7 +440,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -554,7 +546,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -696,7 +688,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -705,17 +697,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6602FAD-A310-49F4-9085-1E788FDA3282}">
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="44" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.453125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="46.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.1796875" style="1" hidden="1"/>
+    <col min="3" max="3" width="40.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -730,7 +722,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
@@ -748,7 +740,7 @@
         <v>SP_IFRS_STAGE_CONFIG_DEV</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -764,7 +756,7 @@
         <v>SP_IFRS_PD_RULES_CONFIG_DEV</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="2" t="s">
         <v>10</v>
@@ -780,9 +772,9 @@
         <v>SP_IFRS_EAD_RULES_CONFIG_DEV</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -796,9 +788,9 @@
         <v>SP_IFRS_LIFETIME_RULES_CONFIG_DEV</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -812,9 +804,9 @@
         <v>SP_IFRS_EIL_MODEL_DETAIL_EAD_DEV</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -828,9 +820,9 @@
         <v>SP_IFRS_EIL_MODEL_DETAIL_LGD_DEV</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -844,9 +836,9 @@
         <v>SP_IFRS_EIL_MODEL_DETAIL_PD_DEV</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -860,9 +852,9 @@
         <v>SP_IFRS_EIL_MODEL_DETAIL_PF_DEV</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -876,9 +868,9 @@
         <v>SP_IFRS_EIL_MODEL_HEADER_DEV</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -892,9 +884,9 @@
         <v>SP_IFRS_LGD_WORKOUT_RULES_CONFIG_DEV</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -908,9 +900,9 @@
         <v>SP_IFRS_LGD_RULES_CONFIG_DEV</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -924,9 +916,9 @@
         <v>SP_IFRS_SEGMENTATION_MAPPING_DEV</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -940,9 +932,9 @@
         <v>SP_IFRS_DEFAULT_CRITERIA_DEV</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -956,9 +948,9 @@
         <v>SP_IFRS_SYNC_PARAM_DEV</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -972,9 +964,9 @@
         <v>SP_IFRS_BUCKET_DETAIL_DEV</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -988,7 +980,7 @@
         <v>SP_IFRS_BUCKET_HEADER_DEV</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>33</v>
       </c>
@@ -1006,7 +998,7 @@
         <v>SP_IFRS_PD_RULE_DATA_DEV</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="1" t="s">
         <v>20</v>
@@ -1022,7 +1014,7 @@
         <v>SP_IFRS_PD_TM_SCENARIO_DATA_DEV</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="1" t="s">
         <v>21</v>
@@ -1038,7 +1030,7 @@
         <v>SP_IFRS_PD_MIGRATION_DETAIL_DEV</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
       <c r="B21" s="1" t="s">
         <v>22</v>
@@ -1054,7 +1046,7 @@
         <v>SP_IFRS_PD_MAA_ENR_DEV</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="1" t="s">
         <v>23</v>
@@ -1070,7 +1062,7 @@
         <v>SP_IFRS_PD_MAA_ENR_SUM_DEV</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="1" t="s">
         <v>24</v>
@@ -1086,7 +1078,7 @@
         <v>SP_IFRS_PD_MAA_FLOWRATE_DEV</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="1" t="s">
         <v>25</v>
@@ -1102,7 +1094,7 @@
         <v>SP_IFRS_PD_MAA_FLOWRATE_SUM_DEV</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
       <c r="B25" s="1" t="s">
         <v>26</v>
@@ -1118,7 +1110,7 @@
         <v>SP_IFRS_PD_MAA_ODR_DEV</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="1" t="s">
         <v>27</v>
@@ -1134,7 +1126,7 @@
         <v>SP_IFRS_PD_MAA_FLOWRATE_SMOOTH_DEV</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="1" t="s">
         <v>28</v>
@@ -1150,7 +1142,7 @@
         <v>SP_IFRS_PD_LINEST_SMOOTHING_DEV</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="1" t="s">
         <v>29</v>
@@ -1166,7 +1158,7 @@
         <v>SP_IFRS_PD_MAA_MMULT_MONTHLY_DEV</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="1" t="s">
         <v>30</v>
@@ -1182,7 +1174,7 @@
         <v>SP_IFRS_PD_MAA_MMULT_DEV</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="1" t="s">
         <v>31</v>
@@ -1198,7 +1190,7 @@
         <v>SP_IFRS_PD_TERM_STRUCTURE_DEV</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
       <c r="B31" s="1" t="s">
         <v>32</v>
@@ -1214,7 +1206,7 @@
         <v>SP_IFRS_PD_SYNC_TERM_STRUCTURE_FL_DEV</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>42</v>
       </c>
@@ -1232,7 +1224,7 @@
         <v>SP_IFRS_EIL_MODEL_DEV</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="1" t="s">
         <v>35</v>
@@ -1248,7 +1240,7 @@
         <v>SP_IFRS_UPDATE_STAGE_DEV</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="1" t="s">
         <v>36</v>
@@ -1264,7 +1256,7 @@
         <v>SP_IFRS_STAGE_BENCANA_DEV</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
       <c r="B35" s="1" t="s">
         <v>37</v>
@@ -1280,7 +1272,7 @@
         <v>SP_IFRS_EIL_GENERATE_IMA_DEV</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
       <c r="B36" s="1" t="s">
         <v>38</v>
@@ -1296,7 +1288,7 @@
         <v>SP_IFRS_EAD_RESULT_DEV</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
       <c r="B37" s="1" t="s">
         <v>39</v>
@@ -1312,7 +1304,7 @@
         <v>SP_IFRS_EIL_RESULT_DETAIL_DEV</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
       <c r="B38" s="1" t="s">
         <v>40</v>
@@ -1328,7 +1320,7 @@
         <v>SP_IFRS_EIL_RESULT_HEADER_DEV</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
       <c r="B39" s="1" t="s">
         <v>41</v>
